--- a/30.publish/서점등록/서점등록_등록콘텐츠_웹서비스가이드.xlsx
+++ b/30.publish/서점등록/서점등록_등록콘텐츠_웹서비스가이드.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>시놀로지NAS</t>
+          <t>홈서버구축</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr"/>
@@ -783,7 +783,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>서버비용절약</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>NAS활용법</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr"/>
@@ -809,7 +809,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>토스페이먼츠</t>
+          <t>1인창업IT</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>웹서비스구축</t>
+          <t>개인웹서비스</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>NAS웹서버  Cloudflare Tunnel  RBAC  전자책  IT가이드</t>
+          <t>홈서버  무료서버구축  소자본창업  온라인결제구축  회원시스템  자체서버운영</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1102,8 +1102,8 @@
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A16:C16"/>
     <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/30.publish/서점등록/서점등록_등록콘텐츠_웹서비스가이드.xlsx
+++ b/30.publish/서점등록/서점등록_등록콘텐츠_웹서비스가이드.xlsx
@@ -963,7 +963,7 @@
       <c r="B29" s="3" t="n"/>
       <c r="C29" s="4" t="n"/>
     </row>
-    <row r="30" ht="15" customHeight="1">
+    <row r="30" ht="260" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
           <t>저자 소개</t>
@@ -971,7 +971,24 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>이인성 | WorksFree 운영자. Synology NAS 기반 풀스택 웹서비스를 직접 설계·운영하며 축적한 실전 노하우를 공유합니다. worksfree.kr</t>
+          <t>이인성 | WorksFree 운영자
+[자격 · 전문성]
+▪ 경영지도사 (생산관리분야)
+▪ 프로젝트 관리 전문가 PMP (PMI)
+▪ IITP 평가위원 / NIPA 평가위원
+▪ KOIIA DX/AX 진단 컨설팅 위원
+▪ 2025년 예비창업패키지 1·2단계 선정 및 수행
+[경력]
+▪ 자동화 장비 제조업 프로세스 개선 내부 컨설팅
+▪ 소프트웨어 분야 개발 및 PM
+▪ 제조업 설계 및 MCT 단순 반복 업무 자동화 프로그램 개발
+  · 어셈블리 BOM 엑셀 저장 자동화 프로그램
+  · 8만여 개 구매품 속성 2주만에 정리하기
+  · 이드로잉스 뷰어 대량 출력 자동화 프로그램
+  · 구글 드라이브 기반 인터넷 정보 자동 업데이트
+  · RPA 프로그램 상세: www.worksfree.com
+Synology NAS 기반 풀스택 웹서비스를 직접 설계·운영하며
+축적한 실전 노하우를 공유합니다. worksfree.kr</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr"/>
